--- a/optimized_version/metadata/testing_daily_metrics/agus4_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus4_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02020697439652537</v>
+        <v>0.01804447903943425</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02418859704556553</v>
+        <v>0.02159999927832246</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02418859704556553</v>
+        <v>0.02159999927832246</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8036148225699998</v>
+        <v>0.8034442054172231</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9243323830871309</v>
+        <v>0.9241166666065274</v>
       </c>
       <c r="F3" t="n">
-        <v>2.885330202126227</v>
+        <v>2.885322529052202</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.065506411635938</v>
+        <v>-1.065495425882895</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1402172721647644</v>
+        <v>0.1403985525205997</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1680842835795389</v>
+        <v>0.1683000000601425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2124312959786753</v>
+        <v>0.2124358334550445</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8083115836426462</v>
+        <v>-0.808388834583204</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>4.30047036172565</v>
+        <v>4.300115692154685</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4.484427266174258</v>
+        <v>4.483995833213051</v>
       </c>
       <c r="F5" t="n">
-        <v>8.472675928708929</v>
+        <v>8.472490635061794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7728396645730047</v>
+        <v>0.7728496002549852</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9798355325570817</v>
+        <v>0.9796723453517278</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.242061549753797</v>
+        <v>1.241845833273193</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701230874831707</v>
+        <v>2.701411442511522</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07762724458546988</v>
+        <v>0.07750392578544907</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1228855025953294</v>
+        <v>0.1225541385790162</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1593647661742684</v>
+        <v>0.1589333332130612</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2362344872374908</v>
+        <v>0.2361628569280868</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1266833699642367</v>
+        <v>-0.1260002144790251</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>0.153759637224089</v>
+        <v>0.1535954872982652</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2002073830871289</v>
+        <v>0.1999916666065253</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2394545276507227</v>
+        <v>0.2394791366281292</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.201509436608452</v>
+        <v>-1.20196196244226</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>6.743770055829945</v>
+        <v>6.744855167373349</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.576949634318147</v>
+        <v>6.577812500240562</v>
       </c>
       <c r="F9" t="n">
-        <v>13.52718536756714</v>
+        <v>13.52758419837999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5432305936066908</v>
+        <v>0.5432036587500653</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>1.843878054831949</v>
+        <v>1.8444719733305</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.371739400492408</v>
+        <v>1.372170833453615</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609124069104228</v>
+        <v>2.609166326877871</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4792652120551774</v>
+        <v>0.479248344117576</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>1.272407804594502</v>
+        <v>1.271899663804031</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9874022661742577</v>
+        <v>0.9869708332130506</v>
       </c>
       <c r="F11" t="n">
-        <v>1.966562107175563</v>
+        <v>1.966226773556615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7172995580496142</v>
+        <v>0.7173959606798508</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>1.809815368606224</v>
+        <v>1.808610855740401</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.995306798522781</v>
+        <v>1.994012499639159</v>
       </c>
       <c r="F12" t="n">
-        <v>3.892662458184544</v>
+        <v>3.891412335461329</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9606194333708264</v>
+        <v>0.9606447233293408</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4566965313885276</v>
+        <v>0.4571844907303683</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6071361840719488</v>
+        <v>0.6077833335137596</v>
       </c>
       <c r="F13" t="n">
-        <v>1.657317733350945</v>
+        <v>1.657364573163819</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6746968544928165</v>
+        <v>0.6746784665235388</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5951817450439489</v>
+        <v>0.5950208031309807</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7616032164204611</v>
+        <v>0.7613874999398575</v>
       </c>
       <c r="F14" t="n">
-        <v>1.37167047870711</v>
+        <v>1.371701124449844</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.820669513116365</v>
+        <v>-0.8207508685055209</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>0.161784139046957</v>
+        <v>0.1612861649865758</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2095638159280568</v>
+        <v>0.2089166664862461</v>
       </c>
       <c r="F15" t="n">
-        <v>0.258601310150449</v>
+        <v>0.2583853113808962</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.075805226724312</v>
+        <v>-1.072339009776751</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>0.136681588891947</v>
+        <v>0.1368492022426695</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1766092835795353</v>
+        <v>0.1768250000601389</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2062756053669831</v>
+        <v>0.2065597210685133</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02343165058221353</v>
+        <v>0.02073962617922553</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1470810878096246</v>
+        <v>0.1471411504280132</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1900416666666681</v>
+        <v>0.1901166667268086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2352419995895103</v>
+        <v>0.2351586007164779</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8409599996046242</v>
+        <v>-0.8396549029483231</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1731880811630999</v>
+        <v>0.1731896424183541</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -893,10 +893,10 @@
         <v>0.2244708333333326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2628794499186585</v>
+        <v>0.2628831576684676</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1996734359766712</v>
+        <v>-0.1997072774985049</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>3.374118184871272</v>
+        <v>3.374357854238923</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3.376267616912868</v>
+        <v>3.376483333393472</v>
       </c>
       <c r="F19" t="n">
-        <v>7.823148862048424</v>
+        <v>7.823478533221222</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7834429226074532</v>
+        <v>0.7834246705886817</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7518331934887594</v>
+        <v>0.7516534285600206</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8990157163234495</v>
+        <v>0.8987999999398587</v>
       </c>
       <c r="F20" t="n">
-        <v>2.784869786211257</v>
+        <v>2.784109307687915</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8912783419184119</v>
+        <v>0.8913377121607211</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2867001674873124</v>
+        <v>0.2863645496574092</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3662897661742595</v>
+        <v>0.365858333214985</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6979673085664221</v>
+        <v>0.6971939015565809</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9071351927469762</v>
+        <v>0.907340882897269</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2190750031054064</v>
+        <v>0.2195768607076613</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2900320174052713</v>
+        <v>0.2906791668335913</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8777874476127321</v>
+        <v>0.8773610456271431</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6941333851383085</v>
+        <v>0.6944304740400435</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>1.673672026520173</v>
+        <v>1.673340980911067</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.082773099514867</v>
+        <v>2.082341666569235</v>
       </c>
       <c r="F23" t="n">
-        <v>5.831343387944769</v>
+        <v>5.831327368928448</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7004210234794392</v>
+        <v>0.7004226693965475</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1358150794167701</v>
+        <v>0.1359770286276842</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1826342835480096</v>
+        <v>0.1828499999311077</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2221247835215129</v>
+        <v>0.2222686307051759</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7113684240117832</v>
+        <v>-0.7135856933797289</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>0.09308143319264241</v>
+        <v>0.09308229513150684</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1249999999999976</v>
+        <v>0.124999999996587</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1491999479399434</v>
+        <v>0.1491009752713564</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3051727443540864</v>
+        <v>0.3060942741470448</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1230365090747819</v>
+        <v>0.1230439026972109</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1647916666666636</v>
+        <v>0.164800000058662</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2017465557709459</v>
+        <v>0.2020571124830334</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.866918202812554</v>
+        <v>-1.875751324710241</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3521096449367832</v>
+        <v>0.3516384715142609</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.473409649688243</v>
+        <v>0.4727625018058366</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9850526174129189</v>
+        <v>0.9847003137288338</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4440835933198711</v>
+        <v>0.4444811687824755</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2748280165052124</v>
+        <v>0.2742091360320553</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3764920328238818</v>
+        <v>0.3756291686476594</v>
       </c>
       <c r="F28" t="n">
-        <v>1.060508029514933</v>
+        <v>1.060339759222458</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.06411204260660375</v>
+        <v>-0.06377438511775058</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2495960700025804</v>
+        <v>0.2499087820772602</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3368560672148568</v>
+        <v>0.3372875003884689</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7529261333506455</v>
+        <v>0.7537867923311733</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9036520869808674</v>
+        <v>0.9034316932747976</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>0.08922338910935891</v>
+        <v>0.08938667631037317</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1185801169516717</v>
+        <v>0.1187958336243303</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1480017108159048</v>
+        <v>0.1476694859876614</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4637286063294308</v>
+        <v>0.4661334799833291</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3041327829561054</v>
+        <v>0.3035188668388855</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4198878656721519</v>
+        <v>0.4190249997163136</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8727774498919063</v>
+        <v>0.8717911081453465</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9325733935659342</v>
+        <v>0.9327257075312472</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1783602825431799</v>
+        <v>0.1786672217858215</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2516810671590808</v>
+        <v>0.252112500120288</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4443288971501579</v>
+        <v>0.4443407518502118</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7819906433243529</v>
+        <v>-0.7820857316542733</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1107985909862268</v>
+        <v>0.1106475520348129</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1565407164204634</v>
+        <v>0.1563249999398598</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2242909686588901</v>
+        <v>0.2243293096617778</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.08107095969103528</v>
+        <v>-0.08144059461459752</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>4.009823446736418</v>
+        <v>4.010000473504437</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.388945833333334</v>
+        <v>4.389154166726808</v>
       </c>
       <c r="F34" t="n">
-        <v>12.03397406155384</v>
+        <v>12.03397430567253</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4994063749932641</v>
+        <v>0.4994063546833876</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1506772249744736</v>
+        <v>0.1505256035811783</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2097907164204642</v>
+        <v>0.2095749999398606</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4141822099963661</v>
+        <v>0.4148816439623074</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8838331875568991</v>
+        <v>0.8834405119802694</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>0.08412605304733202</v>
+        <v>0.08428304769789247</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1163119502462019</v>
+        <v>0.1165276667268055</v>
       </c>
       <c r="F36" t="n">
-        <v>0.151656540070411</v>
+        <v>0.151600538921129</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3244257883273651</v>
+        <v>0.3249246253324862</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.04935770461697984</v>
+        <v>0.04951373498744466</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.06818311691286638</v>
+        <v>0.06839883339346997</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08447206615257469</v>
+        <v>0.08483073930759628</v>
       </c>
       <c r="G37" t="n">
-        <v>0.569886000234531</v>
+        <v>0.5662256691298737</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>0.09270760805947079</v>
+        <v>0.09286492476471488</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1280384502462037</v>
+        <v>0.128254166725822</v>
       </c>
       <c r="F38" t="n">
-        <v>0.148447272398961</v>
+        <v>0.1485614730006256</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0391349844521669</v>
+        <v>-0.04073441413405776</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1583533316123628</v>
+        <v>0.1587646105013521</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2174644004924081</v>
+        <v>0.2180291668470886</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4653517915240871</v>
+        <v>0.4653932400984052</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5925740615231072</v>
+        <v>-0.592857773180733</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1068230060666668</v>
+        <v>0.1065113755569838</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1476189328409241</v>
+        <v>0.1471874998797169</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1648028835609678</v>
+        <v>0.1645085268048715</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5697614786928087</v>
+        <v>-0.5641589402911025</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1125026782329392</v>
+        <v>0.1121917124986769</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1553939328409252</v>
+        <v>0.154962499879718</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1857213768855945</v>
+        <v>0.1856229926715688</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1484343971004007</v>
+        <v>-0.1472179739801538</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2692271918447749</v>
+        <v>0.2693857218626102</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3738509502461997</v>
+        <v>0.3740666667268033</v>
       </c>
       <c r="F42" t="n">
-        <v>0.626853034827242</v>
+        <v>0.626979856006442</v>
       </c>
       <c r="G42" t="n">
-        <v>0.315111843203532</v>
+        <v>0.314834690170305</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1155277853092982</v>
+        <v>0.1154325277032357</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1590323830871311</v>
+        <v>0.1589000000601395</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2003601147234795</v>
+        <v>0.2003375776017846</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.110850851807075</v>
+        <v>-1.110376008527594</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>0.08494957790803635</v>
+        <v>0.08510687994308674</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1171384502462007</v>
+        <v>0.1173541667268043</v>
       </c>
       <c r="F44" t="n">
-        <v>0.142812658162351</v>
+        <v>0.1426512749295361</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2899825659473494</v>
+        <v>-0.2870687635817526</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>0.179838118610839</v>
+        <v>0.1796308063608602</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2479772661742624</v>
+        <v>0.2476874999398622</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5609826901057289</v>
+        <v>0.5608988242252817</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.4748423097994383</v>
+        <v>-0.4744013703359637</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>0.172123230329081</v>
+        <v>0.1722810855087683</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2383676169128641</v>
+        <v>0.2385833333934677</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3459700725966595</v>
+        <v>0.3458247129069335</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.3620900568118168</v>
+        <v>-0.3609457301186416</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>4.554119519149716</v>
+        <v>4.554388202608121</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>4.919446783579535</v>
+        <v>4.919662500060139</v>
       </c>
       <c r="F47" t="n">
-        <v>9.417767966479662</v>
+        <v>9.417775866924563</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7633586381806621</v>
+        <v>0.7633582411496818</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>0.09870263831593439</v>
+        <v>0.09885401368981556</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1365166666666676</v>
+        <v>0.1367250000601411</v>
       </c>
       <c r="F48" t="n">
-        <v>0.175633428410421</v>
+        <v>0.1755574692071811</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.623072771639935</v>
+        <v>-1.620804371668512</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08687691033685019</v>
+        <v>0.08687768382642909</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1699,10 +1699,10 @@
         <v>0.1203416666666683</v>
       </c>
       <c r="F49" t="n">
-        <v>0.151740753947313</v>
+        <v>0.1516623579817052</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5199088777300662</v>
+        <v>-0.5183387795103864</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1566489882286318</v>
+        <v>0.1563410767850805</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2197272661742578</v>
+        <v>0.2192958332130507</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4341288295390872</v>
+        <v>0.4335327018895681</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8551828774165279</v>
+        <v>0.8555803180516248</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>0.05535300508415332</v>
+        <v>0.05515369064639146</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.07797309950758564</v>
+        <v>0.07769166660651905</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1047420752019738</v>
+        <v>0.1048130389360599</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.01613142512315324</v>
+        <v>-0.01750876860607131</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>0.08962261608070657</v>
+        <v>0.08870675670491646</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1263859651894469</v>
+        <v>0.1250916663053327</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1583372070463547</v>
+        <v>0.1577632401769817</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7218756125077299</v>
+        <v>0.7238883403153605</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>0.06429288373644429</v>
+        <v>0.06490285652011782</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.09103296765148272</v>
+        <v>0.09189583357389708</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1158729220650317</v>
+        <v>0.1160199345789626</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.7272763398030779</v>
+        <v>-0.731662046466754</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08369104609032754</v>
+        <v>0.08399793494782236</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1180685671590768</v>
+        <v>0.1185000001189197</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1520252203588555</v>
+        <v>0.1525703527797936</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6353368594332922</v>
+        <v>0.6327169505723753</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>0.08424548130847961</v>
+        <v>0.08398708682363479</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1185605995075913</v>
+        <v>0.1181958332731909</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1809174207864547</v>
+        <v>0.1810950154011022</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2231077248308349</v>
+        <v>-0.2255101906413537</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>0.03710385706909478</v>
+        <v>0.03649066208439004</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.05219203234851714</v>
+        <v>0.05132916642610278</v>
       </c>
       <c r="F56" t="n">
-        <v>0.07211363989490215</v>
+        <v>0.071717149757241</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5978087917941045</v>
+        <v>0.602219232552351</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9945858964808547</v>
+        <v>0.9952249429172104</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.38596213431815</v>
+        <v>1.386825000240564</v>
       </c>
       <c r="F57" t="n">
-        <v>2.37123674124144</v>
+        <v>2.371695675694657</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5853048829397653</v>
+        <v>0.5851443453681574</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>1.108027963166357</v>
+        <v>1.108044157966669</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1933,10 +1933,10 @@
         <v>1.502637499999998</v>
       </c>
       <c r="F58" t="n">
-        <v>2.846843097755043</v>
+        <v>2.846419605061717</v>
       </c>
       <c r="G58" t="n">
-        <v>0.693679228797799</v>
+        <v>0.6937703577818219</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>1.06806247381917</v>
+        <v>1.067304454200189</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.426174415435651</v>
+        <v>1.425095833032633</v>
       </c>
       <c r="F59" t="n">
-        <v>3.810149944912897</v>
+        <v>3.810192187121273</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3958803128811743</v>
+        <v>-0.3959112646257319</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2616539070017893</v>
+        <v>0.2617981719115952</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3572416666666669</v>
+        <v>0.3574416667268068</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8550108123548938</v>
+        <v>0.8556381372798414</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8970466854491596</v>
+        <v>0.8968955554924493</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3677552965018334</v>
+        <v>0.3677638758628083</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2011,10 +2011,10 @@
         <v>0.5106375000000026</v>
       </c>
       <c r="F61" t="n">
-        <v>1.056828632658915</v>
+        <v>1.056620130950105</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6507753972957049</v>
+        <v>0.6509131807384372</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>0.08584642886982466</v>
+        <v>0.08553287542955992</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1177272661742599</v>
+        <v>0.1172958332130527</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2002672823928514</v>
+        <v>0.2004779882565885</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6070013943010254</v>
+        <v>0.6061739933265429</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3333952571603787</v>
+        <v>0.3332409306087523</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4666448830871275</v>
+        <v>0.4664291666065239</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9954305937771629</v>
+        <v>0.9953382764336773</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8264157649765348</v>
+        <v>0.8264479602746659</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1869538336753802</v>
+        <v>0.1868068421678709</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.260699049753794</v>
+        <v>0.2604833332731905</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4735756636791691</v>
+        <v>0.4729602710212287</v>
       </c>
       <c r="G64" t="n">
-        <v>0.860875617289931</v>
+        <v>0.8612369555209929</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2022845137656371</v>
+        <v>0.2016736322937661</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2867545323485198</v>
+        <v>0.2858916664261055</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6261954669730563</v>
+        <v>0.6261700151793068</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.6052175906234674</v>
+        <v>-0.605087104732392</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>3.138187867436297</v>
+        <v>3.138358068534552</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>3.940121783579535</v>
+        <v>3.940337500060139</v>
       </c>
       <c r="F66" t="n">
-        <v>8.214874670472115</v>
+        <v>8.214878780528089</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.3834210764770805</v>
+        <v>-0.3834224607804837</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>0.07193910290483613</v>
+        <v>0.07203455457513555</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.101200000000001</v>
+        <v>0.1013333333934743</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1265992381526272</v>
+        <v>0.1264093943837945</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.2587245055501002</v>
+        <v>-0.2549522579634989</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>0.08027401775124594</v>
+        <v>0.08042847136125195</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1129217835795409</v>
+        <v>0.1131375000601444</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1357543812821569</v>
+        <v>0.1359156003950475</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3252932550235713</v>
+        <v>0.3236897677297477</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>0.06892965358695316</v>
+        <v>0.06908354725048538</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.09674678357953326</v>
+        <v>0.09696250006013685</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1202086580366468</v>
+        <v>0.120322768216106</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3639291999293094</v>
+        <v>0.3627210240079983</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>0.08599980238698594</v>
+        <v>0.08626105913165795</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1206801169128688</v>
+        <v>0.121045833453613</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1542969254446195</v>
+        <v>0.1542524864674102</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.1695166035876663</v>
+        <v>-0.168843036861549</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>0.06142387774377071</v>
+        <v>0.06157809637059245</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0862280335795423</v>
+        <v>0.08644375006014589</v>
       </c>
       <c r="F71" t="n">
-        <v>0.09974631522212302</v>
+        <v>0.09997916300743732</v>
       </c>
       <c r="G71" t="n">
-        <v>0.002603669813357579</v>
+        <v>-0.00205840914848765</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>0.05010547236651827</v>
+        <v>0.05051457705852985</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.07031231715907538</v>
+        <v>0.07088541684708716</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0900298525866368</v>
+        <v>0.08997854662896136</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1819650338443328</v>
+        <v>0.1828971270834862</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7927486030300284</v>
+        <v>0.7921492163303264</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.068583699015189</v>
+        <v>1.067720833092775</v>
       </c>
       <c r="F73" t="n">
-        <v>3.391573156782616</v>
+        <v>3.391562097259069</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0851260052288747</v>
+        <v>-0.08511892830233636</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1179683761338346</v>
+        <v>0.1179692306011682</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2349,10 +2349,10 @@
         <v>0.1656249999999998</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1921662199091018</v>
+        <v>0.1924361929683455</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4651218700964583</v>
+        <v>0.4636179208559263</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>0.07806561556260153</v>
+        <v>0.07837438661910091</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.10931856715908</v>
+        <v>0.1097500001202872</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1284922268131016</v>
+        <v>0.128733195579654</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.1616144774231905</v>
+        <v>-0.1659754459108826</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>0.07611811519741245</v>
+        <v>0.0756516537108214</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1066836990151856</v>
+        <v>0.1060291664862447</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1313103086014629</v>
+        <v>0.1307956268608567</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6186264274320694</v>
+        <v>0.6216102195883688</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>0.7892149241884207</v>
+        <v>0.7889079772910916</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.06334393284093</v>
+        <v>1.062912499879722</v>
       </c>
       <c r="F77" t="n">
-        <v>3.395338132998749</v>
+        <v>3.395339608137603</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.08949481929205638</v>
+        <v>-0.08949576597625986</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>0.05528419089264118</v>
+        <v>0.05558689298896532</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.07758845024619869</v>
+        <v>0.07801250012027576</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1062127618454593</v>
+        <v>0.1061227885354567</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6868191432095371</v>
+        <v>0.6873495123102851</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>0.07353914581270894</v>
+        <v>0.07384723416351976</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1030394004924062</v>
+        <v>0.1034708334536134</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1305878094960222</v>
+        <v>0.1309395488161665</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2112194714761799</v>
+        <v>0.2069645754293927</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1410460205766499</v>
+        <v>0.1408886291076554</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1975730995075911</v>
+        <v>0.1973499999398574</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3296921004386915</v>
+        <v>0.3295960150080784</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5514163516508144</v>
+        <v>-0.5505121941914448</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>0.08289478232332273</v>
+        <v>0.08258896911049926</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1165105995075966</v>
+        <v>0.1160791665463895</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1473187715283633</v>
+        <v>0.1472215379755437</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.305063531324121</v>
+        <v>-0.3033413599340211</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>0.09562372066197188</v>
+        <v>0.09563056609410668</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1345125000000055</v>
+        <v>0.1345208333934794</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1687956972700242</v>
+        <v>0.1689329194230355</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.4929333620240137</v>
+        <v>-0.4953617035667173</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>0.04789198117576307</v>
+        <v>0.04781233033351101</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0673734172628515</v>
+        <v>0.06726086953384093</v>
       </c>
       <c r="F83" t="n">
-        <v>0.08139469051961204</v>
+        <v>0.0812205986566777</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.4868175205318448</v>
+        <v>-0.4804641327118724</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/testing_daily_metrics/agus4_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus4_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01804447903943425</v>
+        <v>0.01804447997055092</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02159999927832246</v>
+        <v>0.02160000039290821</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02159999927832246</v>
+        <v>0.02160000039290821</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8034442054172231</v>
+        <v>0.8034442054906865</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9241166666065274</v>
+        <v>0.9241166666994095</v>
       </c>
       <c r="F3" t="n">
-        <v>2.885322529052202</v>
+        <v>2.885322529055006</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.065495425882895</v>
+        <v>-1.065495425886909</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1403985525205997</v>
+        <v>0.1403985524425448</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1683000000601425</v>
+        <v>0.1682999999672603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2124358334550445</v>
+        <v>0.2124358334463001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.808388834583204</v>
+        <v>-0.8083888344343266</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>4.300115692154685</v>
+        <v>4.300115692307395</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4.483995833213051</v>
+        <v>4.483995833398815</v>
       </c>
       <c r="F5" t="n">
-        <v>8.472490635061794</v>
+        <v>8.472490635141407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7728496002549852</v>
+        <v>0.7728496002507164</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9796723453517278</v>
+        <v>0.9796723454219921</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.241845833273193</v>
+        <v>1.241845833366076</v>
       </c>
       <c r="F6" t="n">
-        <v>2.701411442511522</v>
+        <v>2.701411442433243</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07750392578544907</v>
+        <v>0.07750392583891197</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1225541385790162</v>
+        <v>0.1225541387216933</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1589333332130612</v>
+        <v>0.1589333333988255</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2361628569280868</v>
+        <v>0.2361628569528252</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1260002144790251</v>
+        <v>-0.1260002147149253</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1535954872982652</v>
+        <v>0.1535954873689441</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1999916666065253</v>
+        <v>0.1999916666994075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2394791366281292</v>
+        <v>0.2394791366115098</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.20196196244226</v>
+        <v>-1.201961962136636</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>6.744855167373349</v>
+        <v>6.744855166906127</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.577812500240562</v>
+        <v>6.577812499869033</v>
       </c>
       <c r="F9" t="n">
-        <v>13.52758419837999</v>
+        <v>13.52758419820816</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5432036587500653</v>
+        <v>0.5432036587616699</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>1.8444719733305</v>
+        <v>1.844471973074773</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1.372170833453615</v>
+        <v>1.372170833267851</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609166326877871</v>
+        <v>2.609166326859123</v>
       </c>
       <c r="G10" t="n">
-        <v>0.479248344117576</v>
+        <v>0.4792483441250597</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>1.271899663804031</v>
+        <v>1.271899664022824</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9869708332130506</v>
+        <v>0.9869708333988149</v>
       </c>
       <c r="F11" t="n">
-        <v>1.966226773556615</v>
+        <v>1.966226773700279</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7173959606798508</v>
+        <v>0.7173959606385532</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>1.808610855740401</v>
+        <v>1.808610856259034</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.994012499639159</v>
+        <v>1.994012500196452</v>
       </c>
       <c r="F12" t="n">
-        <v>3.891412335461329</v>
+        <v>3.891412335999317</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9606447233293408</v>
+        <v>0.9606447233184591</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4571844907303683</v>
+        <v>0.4571844905202651</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6077833335137596</v>
+        <v>0.6077833332351131</v>
       </c>
       <c r="F13" t="n">
-        <v>1.657364573163819</v>
+        <v>1.657364573142781</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6746784665235388</v>
+        <v>0.674678466531798</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5950208031309807</v>
+        <v>0.5950208032002784</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7613874999398575</v>
+        <v>0.7613875000327397</v>
       </c>
       <c r="F14" t="n">
-        <v>1.371701124449844</v>
+        <v>1.371701124435597</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8207508685055209</v>
+        <v>-0.8207508684676996</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1612861649865758</v>
+        <v>0.161286165200991</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2089166664862461</v>
+        <v>0.2089166667648925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2583853113808962</v>
+        <v>0.2583853114683556</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.072339009776751</v>
+        <v>-1.07233901117966</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1368492022426695</v>
+        <v>0.1368492021704993</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1768250000601389</v>
+        <v>0.1768249999672567</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2065597210685133</v>
+        <v>0.2065597209392803</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02073962617922553</v>
+        <v>0.0207396274045637</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1471411504280132</v>
+        <v>0.1471411503552823</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1901166667268086</v>
+        <v>0.1901166666339265</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2351586007164779</v>
+        <v>0.2351586007462591</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8396549029483231</v>
+        <v>-0.8396549034142831</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1731896424183541</v>
+        <v>0.1731896424176818</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -893,10 +893,10 @@
         <v>0.2244708333333326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2628831576684676</v>
+        <v>0.2628831576613835</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1997072774985049</v>
+        <v>-0.199707277433846</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>3.374357854238923</v>
+        <v>3.374357854135728</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>3.376483333393472</v>
+        <v>3.37648333330059</v>
       </c>
       <c r="F19" t="n">
-        <v>7.823478533221222</v>
+        <v>7.823478533079092</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7834246705886817</v>
+        <v>0.7834246705965509</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7516534285600206</v>
+        <v>0.7516534286461218</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8987999999398587</v>
+        <v>0.8988000000436548</v>
       </c>
       <c r="F20" t="n">
-        <v>2.784109307687915</v>
+        <v>2.784109308015584</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8913377121607211</v>
+        <v>0.8913377121351436</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2863645496574092</v>
+        <v>0.2863645497994025</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.365858333214985</v>
+        <v>0.365858333397604</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6971939015565809</v>
+        <v>0.6971939018890109</v>
       </c>
       <c r="G21" t="n">
-        <v>0.907340882897269</v>
+        <v>0.9073408828089071</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2195768607076613</v>
+        <v>0.2195768604245524</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2906791668335913</v>
+        <v>0.2906791664689976</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8773610456271431</v>
+        <v>0.8773610458402883</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6944304740400435</v>
+        <v>0.694430473891574</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>1.673340980911067</v>
+        <v>1.673340981231557</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.082341666569235</v>
+        <v>2.082341667009847</v>
       </c>
       <c r="F23" t="n">
-        <v>5.831327368928448</v>
+        <v>5.831327368597487</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7004226693965475</v>
+        <v>0.700422669430553</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1359770286276842</v>
+        <v>0.1359770286139648</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1828499999311077</v>
+        <v>0.1828499999126905</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2222686307051759</v>
+        <v>0.2222686305316517</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7135856933797289</v>
+        <v>-0.7135856907041509</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>0.09308229513150684</v>
+        <v>0.09308229517441986</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.124999999996587</v>
+        <v>0.1250000000545673</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1491009752713564</v>
+        <v>0.1491009753273536</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3060942741470448</v>
+        <v>0.306094273625831</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1230439026972109</v>
+        <v>0.1230439026856132</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.164800000058662</v>
+        <v>0.1648000000436554</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2020571124830334</v>
+        <v>0.2020571123611993</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.875751324710241</v>
+        <v>-1.875751321242264</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3516384715142609</v>
+        <v>0.3516384703533976</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4727625018058366</v>
+        <v>0.472762500220701</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9847003137288338</v>
+        <v>0.9847003134177434</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4444811687824755</v>
+        <v>0.4444811691334788</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2742091360320553</v>
+        <v>0.2742091359920807</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3756291686476594</v>
+        <v>0.3756291686069216</v>
       </c>
       <c r="F28" t="n">
-        <v>1.060339759222458</v>
+        <v>1.060339758231194</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.06377438511775058</v>
+        <v>-0.06377438312880246</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2499087820772602</v>
+        <v>0.2499087844800715</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3372875003884689</v>
+        <v>0.3372875037168027</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7537867923311733</v>
+        <v>0.753786792109213</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9034316932747976</v>
+        <v>0.9034316933316686</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>0.08938667631037317</v>
+        <v>0.08938667837863355</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1187958336243303</v>
+        <v>0.1187958363771055</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1476694859876614</v>
+        <v>0.1476694874668787</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4661334799833291</v>
+        <v>0.4661334692877598</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3035188668388855</v>
+        <v>0.3035188671447112</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4190249997163136</v>
+        <v>0.419025000143094</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8717911081453465</v>
+        <v>0.8717911085869119</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9327257075312472</v>
+        <v>0.9327257074630979</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1786672217858215</v>
+        <v>0.1786672216536611</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.252112500120288</v>
+        <v>0.2521124999345237</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4443407518502118</v>
+        <v>0.444340751841861</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7820857316542733</v>
+        <v>-0.7820857315872889</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1106475520348129</v>
+        <v>0.1106475520998465</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1563249999398598</v>
+        <v>0.1563250000327419</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2243293096617778</v>
+        <v>0.2243293096388398</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.08144059461459752</v>
+        <v>-0.08144059439343954</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>4.010000473504437</v>
+        <v>4.01000047342596</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>4.389154166726808</v>
+        <v>4.389154166633926</v>
       </c>
       <c r="F34" t="n">
-        <v>12.03397430567253</v>
+        <v>12.03397430567231</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4994063546833876</v>
+        <v>0.4994063546834063</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1505256035811783</v>
+        <v>0.1505256036464628</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2095749999398606</v>
+        <v>0.2095750000327428</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4148816439623074</v>
+        <v>0.4148816436579253</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8834405119802694</v>
+        <v>0.8834405121512995</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>0.08428304769789247</v>
+        <v>0.08428304763029394</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1165276667268055</v>
+        <v>0.1165276666339234</v>
       </c>
       <c r="F36" t="n">
-        <v>0.151600538921129</v>
+        <v>0.1516005389355841</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3249246253324862</v>
+        <v>0.3249246252037497</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.04951373498744466</v>
+        <v>0.04951373492816004</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.06839883339346997</v>
+        <v>0.06839883331150176</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08483073930759628</v>
+        <v>0.08483073914327917</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5662256691298737</v>
+        <v>0.5662256708103152</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>0.09286492476471488</v>
+        <v>0.09286492469768835</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.128254166725822</v>
+        <v>0.1282541666339251</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1485614730006256</v>
+        <v>0.1485614729458314</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.04073441413405776</v>
+        <v>-0.04073441336634498</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1587646105013521</v>
+        <v>0.1587646102985475</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2180291668470886</v>
+        <v>0.2180291665684422</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4653932400984052</v>
+        <v>0.4653932400774595</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.592857773180733</v>
+        <v>-0.5928577730373554</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1065113755569838</v>
+        <v>0.1065113756911641</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1471874998797169</v>
+        <v>0.1471875000654812</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1645085268048715</v>
+        <v>0.1645085269229584</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5641589402911025</v>
+        <v>-0.56415894253666</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1121917124986769</v>
+        <v>0.112191712632571</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.154962499879718</v>
+        <v>0.1549625000654823</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1856229926715688</v>
+        <v>0.1856229927061701</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1472179739801538</v>
+        <v>-0.1472179744078514</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2693857218626102</v>
+        <v>0.2693857217943512</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3740666667268033</v>
+        <v>0.3740666666339211</v>
       </c>
       <c r="F42" t="n">
-        <v>0.626979856006442</v>
+        <v>0.6269798559495406</v>
       </c>
       <c r="G42" t="n">
-        <v>0.314834690170305</v>
+        <v>0.3148346902946692</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1154325277032357</v>
+        <v>0.115432527659142</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1589000000601395</v>
+        <v>0.1588999999999992</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2003375776017846</v>
+        <v>0.2003375776042882</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.110376008527594</v>
+        <v>-1.11037600858034</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>0.08510687994308674</v>
+        <v>0.08510687987535638</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1173541667268043</v>
+        <v>0.1173541666339221</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1426512749295361</v>
+        <v>0.1426512749889502</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.2870687635817526</v>
+        <v>-0.2870687646538779</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1796308063608602</v>
+        <v>0.1796308064271388</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2476874999398622</v>
+        <v>0.2476875000327444</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5608988242252817</v>
+        <v>0.560898824258823</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.4744013703359637</v>
+        <v>-0.4744013705122996</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1722810855087683</v>
+        <v>0.1722810854407998</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2385833333934677</v>
+        <v>0.2385833333005856</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3458247129069335</v>
+        <v>0.3458247129653634</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.3609457301186416</v>
+        <v>-0.3609457305785273</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>4.554388202608121</v>
+        <v>4.554388202492432</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>4.919662500060139</v>
+        <v>4.919662499967257</v>
       </c>
       <c r="F47" t="n">
-        <v>9.417775866924563</v>
+        <v>9.417775866921007</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7633582411496818</v>
+        <v>0.7633582411498605</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>0.09885401368981556</v>
+        <v>0.09885401362234039</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1367250000601411</v>
+        <v>0.136724999967259</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1755574692071811</v>
+        <v>0.175557469231677</v>
       </c>
       <c r="G48" t="n">
-        <v>-1.620804371668512</v>
+        <v>-1.620804372399885</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>0.08687768382642909</v>
+        <v>0.08687768382609605</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1699,10 +1699,10 @@
         <v>0.1203416666666683</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1516623579817052</v>
+        <v>0.1516623580059573</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.5183387795103864</v>
+        <v>-0.5183387799959775</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1563410767850805</v>
+        <v>0.1563410769176595</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2192958332130507</v>
+        <v>0.2192958333988149</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4335327018895681</v>
+        <v>0.4335327021430947</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8555803180516248</v>
+        <v>0.8555803178827138</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>0.05515369064639146</v>
+        <v>0.05515369071212823</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.07769166660651905</v>
+        <v>0.0776916666994012</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1048130389360599</v>
+        <v>0.1048130388917514</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.01750876860607131</v>
+        <v>-0.01750876774579124</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>0.08870675670491646</v>
+        <v>0.08870675709961133</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1250916663053327</v>
+        <v>0.1250916668631182</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1577632401769817</v>
+        <v>0.1577632404158889</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7238883403153605</v>
+        <v>0.7238883394791068</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>0.06490285652011782</v>
+        <v>0.06490285625747871</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.09189583357389708</v>
+        <v>0.09189583320236849</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1160199345789626</v>
+        <v>0.1160199345032687</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.731662046466754</v>
+        <v>-0.7316620442072055</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>0.08399793494782236</v>
+        <v>0.08399793483297513</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1185000001189197</v>
+        <v>0.1184999999575602</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1525703527797936</v>
+        <v>0.15257035262052</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6327169505723753</v>
+        <v>0.6327169513392148</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>0.08398708682363479</v>
+        <v>0.08398708688922323</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1181958332731909</v>
+        <v>0.1181958333660731</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1810950154011022</v>
+        <v>0.1810950153167059</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2255101906413537</v>
+        <v>-0.2255101894990961</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>0.03649066208439004</v>
+        <v>0.03649066234841654</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.05132916642610278</v>
+        <v>0.05132916679763137</v>
       </c>
       <c r="F56" t="n">
-        <v>0.071717149757241</v>
+        <v>0.07171714990831647</v>
       </c>
       <c r="G56" t="n">
-        <v>0.602219232552351</v>
+        <v>0.602219230876464</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9952249429172104</v>
+        <v>0.9952249426420529</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1.386825000240564</v>
+        <v>1.386824999869036</v>
       </c>
       <c r="F57" t="n">
-        <v>2.371695675694657</v>
+        <v>2.371695675496463</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5851443453681574</v>
+        <v>0.5851443454374936</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>1.108044157966669</v>
+        <v>1.108044157959696</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1933,10 +1933,10 @@
         <v>1.502637499999998</v>
       </c>
       <c r="F58" t="n">
-        <v>2.846419605061717</v>
+        <v>2.846419605243569</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6937703577818219</v>
+        <v>0.693770357742693</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>1.067304454200189</v>
+        <v>1.067304454526573</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1.425095833032633</v>
+        <v>1.425095833497044</v>
       </c>
       <c r="F59" t="n">
-        <v>3.810192187121273</v>
+        <v>3.810192187102706</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3959112646257319</v>
+        <v>-0.3959112646121279</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2617981719115952</v>
+        <v>0.2617981718446628</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3574416667268068</v>
+        <v>0.3574416666339246</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8556381372798414</v>
+        <v>0.855638137008144</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8968955554924493</v>
+        <v>0.8968955555579283</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3677638758628083</v>
+        <v>0.3677638758591143</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2011,10 +2011,10 @@
         <v>0.5106375000000026</v>
       </c>
       <c r="F61" t="n">
-        <v>1.056620130950105</v>
+        <v>1.056620131038524</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6509131807384372</v>
+        <v>0.6509131806800132</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>0.08553287542955992</v>
+        <v>0.08553287556456822</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1172958332130527</v>
+        <v>0.117295833398817</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2004779882565885</v>
+        <v>0.2004779881587156</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6061739933265429</v>
+        <v>0.6061739937110726</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3332409306087523</v>
+        <v>0.3332409306752014</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4664291666065239</v>
+        <v>0.466429166699406</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9953382764336773</v>
+        <v>0.9953382764719795</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8264479602746659</v>
+        <v>0.8264479602613088</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1868068421678709</v>
+        <v>0.1868068422311618</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2604833332731905</v>
+        <v>0.2604833333660726</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4729602710212287</v>
+        <v>0.4729602712833236</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8612369555209929</v>
+        <v>0.8612369553671995</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2016736322937661</v>
+        <v>0.2016736325567965</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.2858916664261055</v>
+        <v>0.2858916667976341</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6261700151793068</v>
+        <v>0.626170015187962</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.605087104732392</v>
+        <v>-0.6050871047767645</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>3.138358068534552</v>
+        <v>3.138358068461267</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>3.940337500060139</v>
+        <v>3.940337499967256</v>
       </c>
       <c r="F66" t="n">
-        <v>8.214878780528089</v>
+        <v>8.214878780526144</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.3834224607804837</v>
+        <v>-0.3834224607798287</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>0.07203455457513555</v>
+        <v>0.07203455450884438</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1013333333934743</v>
+        <v>0.1013333333005922</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1264093943837945</v>
+        <v>0.1264093944541857</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.2549522579634989</v>
+        <v>-0.2549522593611417</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>0.08042847136125195</v>
+        <v>0.08042847129474807</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1131375000601444</v>
+        <v>0.1131374999672623</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1359156003950475</v>
+        <v>0.1359156003150578</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3236897677297477</v>
+        <v>0.3236897685257989</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>0.06908354725048538</v>
+        <v>0.06908354718422259</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.09696250006013685</v>
+        <v>0.0969624999672547</v>
       </c>
       <c r="F69" t="n">
-        <v>0.120322768216106</v>
+        <v>0.1203227681550068</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3627210240079983</v>
+        <v>0.3627210246552113</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>0.08626105913165795</v>
+        <v>0.08626105899901572</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.121045833453613</v>
+        <v>0.1210458332678487</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1542524864674102</v>
+        <v>0.1542524864771951</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.168843036861549</v>
+        <v>-0.1688430370098375</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>0.06157809637059245</v>
+        <v>0.06157809630418976</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08644375006014589</v>
+        <v>0.08644374996726374</v>
       </c>
       <c r="F71" t="n">
-        <v>0.09997916300743732</v>
+        <v>0.09997916289286654</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.00205840914848765</v>
+        <v>-0.002058406851876748</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>0.05051457705852985</v>
+        <v>0.0505145768596371</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.07088541684708716</v>
+        <v>0.07088541656844072</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08997854662896136</v>
+        <v>0.08997854663502595</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1828971270834862</v>
+        <v>0.18289712697334</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>0.7921492163303264</v>
+        <v>0.7921492165884074</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1.067720833092775</v>
+        <v>1.067720833464303</v>
       </c>
       <c r="F73" t="n">
-        <v>3.391562097259069</v>
+        <v>3.391562097263405</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.08511892830233636</v>
+        <v>-0.08511892830511103</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1179692306011682</v>
+        <v>0.1179692306008002</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2349,10 +2349,10 @@
         <v>0.1656249999999998</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1924361929683455</v>
+        <v>0.1924361928446868</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4636179208559263</v>
+        <v>0.46361792154528</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>0.07837438661910091</v>
+        <v>0.07837438648615178</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1097500001202872</v>
+        <v>0.1097499999345229</v>
       </c>
       <c r="F75" t="n">
-        <v>0.128733195579654</v>
+        <v>0.1287331954647898</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.1659754459108826</v>
+        <v>-0.1659754438301628</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0756516537108214</v>
+        <v>0.07565165390940104</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1060291664862447</v>
+        <v>0.1060291667648912</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1307956268608567</v>
+        <v>0.1307956270718724</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6216102195883688</v>
+        <v>0.6216102183674383</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>0.7889079772910916</v>
+        <v>0.7889079774232551</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1.062912499879722</v>
+        <v>1.062912500065487</v>
       </c>
       <c r="F77" t="n">
-        <v>3.395339608137603</v>
+        <v>3.395339608136543</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.08949576597625986</v>
+        <v>-0.08949576597557951</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>0.05558689298896532</v>
+        <v>0.05558689285636369</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.07801250012027576</v>
+        <v>0.07801249993451147</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1061227885354567</v>
+        <v>0.1061227885606197</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6873495123102851</v>
+        <v>0.687349512162019</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>0.07384723416351976</v>
+        <v>0.0738472340308646</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1034708334536134</v>
+        <v>0.1034708332678491</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1309395488161665</v>
+        <v>0.1309395486539023</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2069645754293927</v>
+        <v>0.2069645773948982</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1408886291076554</v>
+        <v>0.1408886291731576</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1973499999398574</v>
+        <v>0.1973500000327396</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3295960150080784</v>
+        <v>0.3295960150450796</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.5505121941914448</v>
+        <v>-0.5505121945395719</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>0.08258896911049926</v>
+        <v>0.08258896924217482</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1160791665463895</v>
+        <v>0.1160791667321538</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1472215379755437</v>
+        <v>0.147221538007625</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3033413599340211</v>
+        <v>-0.3033413605020479</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>0.09563056609410668</v>
+        <v>0.09563056602765148</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1345208333934794</v>
+        <v>0.1345208333005973</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1689329194230355</v>
+        <v>0.1689329193554356</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.4953617035667173</v>
+        <v>-0.4953617023699532</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>0.04781233033351101</v>
+        <v>0.04781233036780667</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.06726086953384093</v>
+        <v>0.06726086958230118</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0812205986566777</v>
+        <v>0.08122059871395608</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.4804641327118724</v>
+        <v>-0.4804641347999776</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
